--- a/levels.xlsx
+++ b/levels.xlsx
@@ -411,112 +411,112 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="str">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
         <v>100</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="str">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
         <v>130</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="str">
         <v>50</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="str">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="str">
         <v>165</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="str">
         <v>125</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
+      <c r="A5" t="str">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="str">
         <v>205</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="str">
         <v>250</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" t="str">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="str">
         <v>250</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="str">
         <v>450</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
+      <c r="A7" t="str">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="str">
         <v>300</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="str">
         <v>700</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
+      <c r="A8" t="str">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="str">
         <v>355</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="str">
         <v>1000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
+      <c r="A9" t="str">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="str">
         <v>415</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="str">
         <v>1350</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
+      <c r="A10" t="str">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="str">
         <v>480</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="str">
         <v>1750</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
+      <c r="A11" t="str">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="str">
         <v>550</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="str">
         <v>2250</v>
       </c>
     </row>

--- a/levels.xlsx
+++ b/levels.xlsx
@@ -397,17 +397,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:B11"/>
+  <cols>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" customWidth="1"/>
+    <col min="16" max="16" width="16.6640625" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" customWidth="1"/>
+    <col min="20" max="20" width="16.6640625" customWidth="1"/>
+    <col min="21" max="21" width="16.6640625" customWidth="1"/>
+    <col min="22" max="22" width="16.6640625" customWidth="1"/>
+    <col min="23" max="23" width="16.6640625" customWidth="1"/>
+    <col min="24" max="24" width="16.6640625" customWidth="1"/>
+    <col min="25" max="25" width="16.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Level</v>
       </c>
       <c r="B1" t="str">
-        <v>HP</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Experience</v>
+        <v>Uses</v>
       </c>
     </row>
     <row r="2">
@@ -415,10 +439,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>100</v>
-      </c>
-      <c r="C2" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -426,10 +447,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>130</v>
-      </c>
-      <c r="C3" t="str">
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -437,10 +455,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>165</v>
-      </c>
-      <c r="C4" t="str">
-        <v>125</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -448,10 +463,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>205</v>
-      </c>
-      <c r="C5" t="str">
-        <v>250</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -459,10 +471,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>250</v>
-      </c>
-      <c r="C6" t="str">
-        <v>450</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -470,10 +479,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>300</v>
-      </c>
-      <c r="C7" t="str">
-        <v>700</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -481,10 +487,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>355</v>
-      </c>
-      <c r="C8" t="str">
-        <v>1000</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -492,10 +495,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>415</v>
-      </c>
-      <c r="C9" t="str">
-        <v>1350</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -503,10 +503,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>480</v>
-      </c>
-      <c r="C10" t="str">
-        <v>1750</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -514,15 +511,12 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>550</v>
-      </c>
-      <c r="C11" t="str">
-        <v>2250</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
   </ignoredErrors>
 </worksheet>
 </file>